--- a/tweets_queue.xlsx
+++ b/tweets_queue.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -848,6 +848,267 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>20+ AI agents in production sounds like a whole lotta overhead, and a whole lotta SaaS bills #smbops</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SaaStr</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Introducing “The Agents”: A New Weekly Show Where We Share Everything Happening With Our 20+ AI Agents in Production. The Good, The Bad, and The Broken.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.saastr.com/introducing-the-agents-a-new-weekly-show-where-we-share-everything-happening-with-our-20-ai-agents-in-production-the-good-the-bad-and-the-broken/</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>140% revenue boost with 1.25 humans and 20 AI agents, but what's the real cost of 'optimizing' your sales team? #salesops</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>SaaStr</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Our 1.25 Humans + 20 AI Agents Closed 140% of What Our All-Human Sales Team Did Last Year. But I’m Not Sure That’s the Real Story.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.saastr.com/our-1-25-humans-20-ai-agents-closed-140-of-what-our-all-human-sales-team-did-last-year-but-im-not-sure-thats-the-real-story/</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>25 minutes to build an app with zero code, but how many SaaS tools did they need to manage it afterwards?</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SaaStr</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>We Shipped a Production App in One Waymo Ride. 25 Minutes. Zero Lines of Code I Wrote Myself.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.saastr.com/we-shipped-a-production-app-in-one-waymo-ride-25-minutes-zero-lines-of-code-i-wrote-myself/</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Too many tools, not enough clarity. Sounds about right. How many SaaS subscriptions is your team juggling? #SMBops</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>9 Best Work Management Software: My Picks for 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/best-work-management-software</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Manual task management is a productivity killer. Automate what you can, focus on what matters #productivityhacks</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneur</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Don’t Manage Every Task Manually — Here’s How You Can Use AI to Outdo Your Competitors in Half the Time</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.entrepreneur.com/leadership/dont-manage-every-task-manually-heres-how-you-can-use/503141</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Liberal arts majors thriving in tech is no surprise - critical thinking and creativity are just as valuable as coding skills #AI</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Entrepreneur</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic Cofounder Majored in English Lit in College. Here’s Why He Says His Degree ‘Turned Out to Be Extremely Relevant.’</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.entrepreneur.com/business-news/anthropic-cofounder-says-his-english-major-was-a-good-idea</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Still waiting for AI to replace my 10 SaaS subscriptions #SMBpain</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/augment-code</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Still paying for separate meeting notes and project tools?</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Fathom 3.0</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/fathom</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>AI-generated carousels are cool, but how many SaaS tools do you need to make one post?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Carousels Generator</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/carousels-generator</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:53 UTC</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tweets_queue.xlsx
+++ b/tweets_queue.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -1109,6 +1109,325 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Most small teams can't afford to build custom AI agents, they're still trying to simplify their SaaS stack #SMBtech</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI updates its Agents SDK to help enterprises build safer, more capable agents</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/15/openai-updates-its-agents-sdk-to-help-enterprises-build-safer-more-capable-agents/</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AI-powered marketing tools are booming, but how many SaaS subs do you need to make it work?</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Hightouch reaches $100M ARR fueled by marketing tools powered by AI</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/15/hightouch-reaches-100m-arr-fueled-by-marketing-tools-powered-by-ai/</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>6+ years out of sales and worried it's too late to get back in? Your skills are rusty, not dead. What's holding you back? #salescomeback</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SaaStr</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Dear SaaStr:  I’ve Been Out of Sales For 6+ Years.  Is It Too Late to Get Back In?</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.saastr.com/dear-saastr-ive-been-out-of-sales-for-6-years-is-it-too-late-to-get-back-in/</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic's $30b revenue with just 5k employees is a wake-up call for bloated startups, no need for 10+ SaaS tools #leanoperations</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SaaStr</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic Only Has ~5,000 Employees. Almost No One Has Ever Been This Efficient. That’s By Choice.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.saastr.com/anthropic-only-has-5000-employees-almost-no-one-has-ever-been-this-efficient-thats-by-choice/</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sales teams: stop throwing discounts at customers. Help them actually use your product and get value from it. That's where the real ROI is #SaaS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SaaStr</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Dear SaaStr:  What Are Some Things Sales Can Do Besides Discounts And Add-Ons to Get a Customer to Buy?</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.saastr.com/dear-saastr-what-are-some-things-sales-can-do-besides-discounts-and-add-ons-to-get-a-customer-to-buy/</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Still trying to manage 10 different SaaS tools while AI chatbots are streamlining workflows #SMBops</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>I Reviewed the 10 Best AI Chatbots Worth Using in 2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/best-ai-chatbots</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Slow mistakes are the worst. Picking the wrong tool can cost you months of productivity, just to fix what's broken instead of shipping what matters #smbops</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>10 Best Automation Testing Tools on G2: My Go-To Picks</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/best-automation-testing-tools</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Scaling teams still using shared folders for brand assets are wasting time, not just storage space #brandmanagement</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>10 Best Brand Asset Management Software for 2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/brand-asset-management-software</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Automation is great, but how many tools do you need to automate your workflow?</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code Routines</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/claude</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Most SMBs don't need AI platforms with 10 features they'll never use. What's the 80/20 for your business? #SMBops</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>DataGrout</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/datagrout-ai</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Flat rates for LLMs, but still paying for 10 other SaaS tools? #SMBpains</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Wafer Pass</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/wafer</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:38 UTC</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tweets_queue.xlsx
+++ b/tweets_queue.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -1428,6 +1428,209 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Hiring's down 20% since 2022, but it's not AI's fault. Interest rates are the real culprit. Guess that means you still need to manage your cash flow closely #smallbusiness</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn data shows AI isn’t to blame for hiring decline… yet</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/15/linkedin-data-shows-ai-isnt-to-blame-for-hiring-decline-yet/</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Still waiting for AI to simplify my SaaS stack, not add to it #SMBtech</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Gemini vs. Perplexity: Which AI Nailed My Prompts Best? (2026)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/perplexity-vs-gemini</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>AI chatbots are drafting emails and writing code, but can they simplify your SaaS stack?</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>I Tested Gemini vs. ChatGPT: Which AI Chatbot is Better?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/gemini-vs-chatgpt</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Another AI chatbot trying to take down ChatGPT. Meanwhile, I'm still trying to simplify my actual workflow #SMBops</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>G2 Learn</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>I Tested DeepSeek vs. ChatGPT: Which is Better in 2026?</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://learn.g2.com/deepseek-vs-chatgpt</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Another app to keep track of, just what small teams need. #productivity</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>The Verge</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Google launches a Gemini AI app on Mac</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/912638/google-gemini-mac-app</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>20 years of building a business and the biggest lesson is likely simplicity - not 10 different SaaS tools #smallbusiness</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Entrepreneur</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>If I Had to Start Over in 2026, Here’s Exactly How I’d Build a Small Business</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.entrepreneur.com/starting-a-business/how-id-build-my-small-business-if-i-had-to-start-over-in/503494</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Still juggling multiple tools to manage your business? I'm over here dreaming of a grid-layout workflow that streamlines everything #SMBops</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Clide</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/clide-the-ai-native-mac-terminal</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
